--- a/data/录取名单.xlsx
+++ b/data/录取名单.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\code\projects\mail-sender\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\PTSFDTZ\projects\mail-sender\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA523B17-9B17-4A0A-9F6F-317844CE5E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3784FD01-106A-48F8-9A2B-E2FBA498E027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9600" yWindow="7335" windowWidth="28800" windowHeight="8550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,13 +28,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>姓名</t>
+  </si>
+  <si>
+    <t>邮箱</t>
+  </si>
+  <si>
+    <t>录取部门</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>邮箱</t>
+    <t>群号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -42,7 +48,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,6 +70,13 @@
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -87,9 +100,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -371,28 +385,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.125" customWidth="1"/>
+    <col min="2" max="2" width="24.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
       <c r="B3" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
 </file>